--- a/rawresource/excels/dungeon.xlsx
+++ b/rawresource/excels/dungeon.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\MServer\rawresource\excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="500" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -73,13 +78,13 @@
     <t>场景列表</t>
   </si>
   <si>
-    <t>num</t>
+    <t>int</t>
   </si>
   <si>
     <t>str</t>
   </si>
   <si>
-    <t>lua</t>
+    <t>array&lt;int&gt;</t>
   </si>
   <si>
     <t>sc</t>
@@ -1521,7 +1526,6 @@
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1"/>
       <c r="E1" t="s">
         <v>1</v>
       </c>
@@ -2077,7 +2081,6 @@
       <c r="B1" t="s">
         <v>60</v>
       </c>
-      <c r="C1"/>
       <c r="E1" t="s">
         <v>39</v>
       </c>
@@ -2385,7 +2388,6 @@
       <c r="B1" t="s">
         <v>73</v>
       </c>
-      <c r="C1"/>
       <c r="F1" t="s">
         <v>74</v>
       </c>
